--- a/output/pdf_financials_xlsx/DPRO.xlsx
+++ b/output/pdf_financials_xlsx/DPRO.xlsx
@@ -431,6 +431,13 @@
   </sheetPr>
   <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/DPRO.xlsx
+++ b/output/pdf_financials_xlsx/DPRO.xlsx
@@ -506,16 +506,16 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-6.814384</v>
+        <v>6.814384</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>-4.490728</v>
+        <v>4.490728</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-5.162851</v>
+        <v>5.162851</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-6.409827</v>
+        <v>6.409827</v>
       </c>
     </row>
     <row r="6">
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-27.700623</v>
+        <v>27.700623</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-24.680445</v>
+        <v>24.680445</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-16.1377</v>
+        <v>16.1377</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-22.112302</v>
+        <v>22.112302</v>
       </c>
     </row>
     <row r="11">
@@ -620,16 +620,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>28.491298</v>
+        <v>-26.909948</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>26.744559</v>
+        <v>-22.616331</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>17.535904</v>
+        <v>-14.739496</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>23.433638</v>
+        <v>-20.790966</v>
       </c>
     </row>
     <row r="12">
@@ -658,16 +658,16 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1489,13 +1489,13 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.680801</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0</v>
+        <v>0.529542</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0</v>
+        <v>1.192074</v>
       </c>
     </row>
     <row r="54">
@@ -3157,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3400,7 +3400,11 @@
           <t>Equipment 7</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -4230,7 +4234,11 @@
           <t>Equipment 8</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -6206,16 +6214,16 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>-6.814384</v>
+        <v>6.814384</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-4.490728</v>
+        <v>4.490728</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-5.162851</v>
+        <v>5.162851</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>-6.409827</v>
+        <v>6.409827</v>
       </c>
     </row>
     <row r="89">
@@ -6630,16 +6638,16 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>-27.700623</v>
+        <v>27.700623</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>-24.680445</v>
+        <v>24.680445</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-16.1377</v>
+        <v>16.1377</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-22.112302</v>
+        <v>22.112302</v>
       </c>
     </row>
     <row r="101">
@@ -7046,7 +7054,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7080,7 +7088,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7116,7 +7124,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7152,7 +7160,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7188,7 +7196,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7226,7 +7234,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7264,7 +7272,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7298,7 +7306,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7334,7 +7342,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7370,7 +7378,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7406,7 +7414,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7440,7 +7448,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7474,7 +7482,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7510,7 +7518,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7546,7 +7554,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7582,7 +7590,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7618,7 +7626,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7654,7 +7662,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7692,7 +7700,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7728,7 +7736,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7764,7 +7772,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7800,7 +7808,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7836,7 +7844,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Shares            Capital       Payments          Warrants                 Deficit          FVTOCI       Operations             Equity</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8179,7 +8187,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Change in fair value of derivative liability 1 5</t>
+          <t>Change in fair value of derivative liability 15</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -8448,23 +8456,23 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2021 1,326,938 $ 81,038,365 $ 6,406,117 $ - $ (52,322,182) $</t>
+          <t>Total Shareholders’ Equity 34,926,239 26,875 87,170 - (5,122) 3,311,024 (27,654,364) (98,483) 447,542 11,040,881 1,748,946 (222,136) 11,376,230 (1,848,018) - 2,021,664 (23,611,810) (3,180) (94,861) 407,716 10,384,145 (1,123,417) 4,056,827 - - 3,776,428 1,182,618 (13,877,473) (175,117)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" s="5" t="n">
-        <v>34.926239</v>
+        <v>4e-06</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>0.136579</v>
+        <v>4.621783</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>-0.33264</v>
+        <v>-0.009944</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -8480,27 +8488,23 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Shares issued for the exercise of stock options 500 51,875 (25,000) - -</t>
+          <t>Exchange on of  Foreign  Operations  136,579 - - - - - - -  447,542  584,121 - - - - - - -  (94,861)  489,260 - - - - - - - -  (9,944)  479,316                                                                                     Differences  Translation                                                     Comprehensive        $          $           $             $                                (Loss) of at - - - - - - - - - - - - - - - - - - - - - - Other Fair Income in FVTOCI (3,180) Value (98,483) (175,117) (609,420)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" s="5" t="n">
-        <v>0.026875</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.434303</v>
+      </c>
+      <c r="F154" s="5" t="n">
+        <v>-0.431123</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>-0.33264</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -8516,27 +8520,23 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>$                                             Accumulated</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Shares issued for the exercise of warrants 662 87,170 - - -</t>
+          <t>Deficit - - - - - - - - - - - - - - - - - - - - - - statements. Accumulated (52,322,182) (27,654,364) (79,976,546) (23,611,810)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" s="5" t="n">
-        <v>0.08717</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-117.465829</v>
+      </c>
+      <c r="F155" s="5" t="n">
+        <v>-13.877473</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>-103.588356</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -8552,12 +8552,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
+          <t>of</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Shares issued for the exercise of RSUs 43,104 2,427,801 (2,427,801) - -</t>
+          <t>of</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -8577,820 +8577,6 @@
         </is>
       </c>
       <c r="H156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Shares issue costs - (5,122) - - -</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" s="5" t="n">
-        <v>-0.005122</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Share-based payments - - 3,311,024 - -</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" s="5" t="n">
-        <v>3.311024</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Net loss - - - - (27,654,364)</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" s="5" t="n">
-        <v>-27.654364</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Change in fair value of equity investments at FVOCI - - - - -</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" s="5" t="n">
-        <v>-0.098483</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G160" s="5" t="n">
-        <v>-0.098483</v>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Translation of foreign operations - - - - -</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" s="5" t="n">
-        <v>0.447542</v>
-      </c>
-      <c r="F161" s="5" t="n">
-        <v>0.447542</v>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Balance at December 31, 2022 1,371,204 $ 83,600,089 $ 7,264,340 $ - $ (79,976,546) $</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" s="5" t="n">
-        <v>11.040881</v>
-      </c>
-      <c r="F162" s="5" t="n">
-        <v>0.584121</v>
-      </c>
-      <c r="G162" s="5" t="n">
-        <v>-0.431123</v>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Shares issued for financing – ATM (“At-the-market”) 26,030 1,748,946 - - -</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" s="5" t="n">
-        <v>1.748946</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Share issue costs - (222,136) - - -</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" s="5" t="n">
-        <v>-0.222136</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Shares issued for financing 512,000 11,376,230 - - -</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" s="5" t="n">
-        <v>11.37623</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Share issue costs - (2,072,886) 224,868 - -</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" s="5" t="n">
-        <v>-1.848018</v>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Shares issued for the exercise of RSUs 60,332 2,640,733 (2,640,733) - -</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Share-based payments -</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" s="5" t="n">
-        <v>2.021664</v>
-      </c>
-      <c r="F168" s="5" t="n">
-        <v>2.021664</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Net loss - - - - (23,611,810)</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" s="5" t="n">
-        <v>-23.61181</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Balance at December 31, 2023 1,969,566 $ 97,070,976 $ 6,870,139 $ - $ (103,588,356) $</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" s="5" t="n">
-        <v>0.407716</v>
-      </c>
-      <c r="F170" s="5" t="n">
-        <v>0.48926</v>
-      </c>
-      <c r="G170" s="5" t="n">
-        <v>-0.434303</v>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Shares issued for financing 1,477,208 10,384,145 - - -</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" s="5" t="n">
-        <v>10.384145</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Share issue costs - (1,632,871) 509,454 - -</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" s="5" t="n">
-        <v>-1.123417</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Shares issued for the exercise of warrants 1,991,668 4,056,827 - - -</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" s="5" t="n">
-        <v>4.056827</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Shares returned to treasury (36,000) - - - -</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Shares issued for the exercise of RSUs 25,353 863,907 (863,907) - -</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Warrants – equity treatment - -</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" s="5" t="n">
-        <v>3.776428</v>
-      </c>
-      <c r="F176" s="5" t="n">
-        <v>3.776428</v>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Share-based payments - - 1,182,618 - -</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" s="5" t="n">
-        <v>1.182618</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Net loss - - - - (13,877,473)</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" s="5" t="n">
-        <v>-13.877473</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Shares Capital Payments Warrants Deficit FVTOCI Operations Equity</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Balance as of December 31, 2024 5,427,795 $ 110,742,984 $ 7,698,304 $ 3,776,428 $ (117,465,829) $</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" s="5" t="n">
-        <v>4.621783</v>
-      </c>
-      <c r="F179" s="5" t="n">
-        <v>0.479316</v>
-      </c>
-      <c r="G179" s="5" t="n">
-        <v>-0.60942</v>
-      </c>
-      <c r="H179" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/DPRO.xlsx
+++ b/output/pdf_financials_xlsx/DPRO.xlsx
@@ -3332,7 +3332,11 @@
           <t>Prepaids and deposits 6</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DPRO.xlsx
+++ b/output/pdf_financials_xlsx/DPRO.xlsx
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>9.516586</v>
+        <v>10.038935</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8.834009999999999</v>
+        <v>9.434943000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.630367</v>
+        <v>4.134987</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7.64562</v>
+        <v>8.165570000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.362001</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.154147</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.143624</v>
       </c>
     </row>
     <row r="71">
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0.08505799999999999</v>
+        <v>0.447059</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.154147</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.143624</v>
       </c>
     </row>
     <row r="72">
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>4.674953</v>
+        <v>4.312952</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2.818563</v>
+        <v>2.664416</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>1.053735</v>
+        <v>0.910111</v>
       </c>
     </row>
     <row r="76">
@@ -2062,13 +2062,13 @@
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>1.25842498209538</v>
+        <v>2.146300365940998</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.05925721739856674</v>
+        <v>0.09260949724381262</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.001348398774514206</v>
+        <v>0.002835238995248238</v>
       </c>
     </row>
     <row r="81">
@@ -2670,16 +2670,16 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.07971300000000001</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.490391</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.167257</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.923037</v>
       </c>
     </row>
     <row r="112">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.004684</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -3115,16 +3115,16 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.07971300000000001</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.490391</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.167257</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.923037</v>
       </c>
     </row>
     <row r="135">
@@ -3134,16 +3134,16 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-16.349031</v>
+        <v>-16.428744</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-18.773654</v>
+        <v>-19.264045</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-11.834271</v>
+        <v>-12.001528</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-23.875719</v>
+        <v>-24.798756</v>
       </c>
     </row>
   </sheetData>
@@ -3774,7 +3774,11 @@
           <t>Lease liabilities 9</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4536,7 +4540,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -5330,7 +5338,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>-0.07971300000000001</v>
       </c>
@@ -5966,7 +5978,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E81" s="5" t="n">
         <v>-0.004684</v>
       </c>
@@ -6356,7 +6372,11 @@
           <t>Director fees 16</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -8026,7 +8046,11 @@
           <t>Director fees 19</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E140" s="5" t="n">
         <v>0.522349</v>
       </c>
